--- a/healthcare_forms/018_pediatric_symptom_checklist--healthcare_forms.xlsx
+++ b/healthcare_forms/018_pediatric_symptom_checklist--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1144,12 +1144,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C66"/>
+  <dimension ref="A1:C58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'headache'}</t>
+          <t>headache</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'headache'}</t>
+          <t>headache</t>
         </is>
       </c>
     </row>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'fever'}</t>
+          <t>fever</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'fever'}</t>
+          <t>fever</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1211,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'cough'}</t>
+          <t>cough</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'cough'}</t>
+          <t>cough</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'rash'}</t>
+          <t>rash</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'rash'}</t>
+          <t>rash</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'fatigue'}</t>
+          <t>fatigue</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'fatigue'}</t>
+          <t>fatigue</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'sore_throat'}</t>
+          <t>sore_throat</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'sore_throat'}</t>
+          <t>sore throat</t>
         </is>
       </c>
     </row>
@@ -1279,12 +1279,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'sore_ears'}</t>
+          <t>sore_ears</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'sore_ears'}</t>
+          <t>sore ears</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_8,_'label':_'diarrhea'}</t>
+          <t>diarrhea</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 8, 'label': 'diarrhea'}</t>
+          <t>diarrhea</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_9,_'label':_'vomiting'}</t>
+          <t>vomiting</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 9, 'label': 'vomiting'}</t>
+          <t>vomiting</t>
         </is>
       </c>
     </row>
@@ -1330,12 +1330,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_10,_'label':_'loss_of_appetite'}</t>
+          <t>loss_of_appetite</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 10, 'label': 'loss_of_appetite'}</t>
+          <t>loss of appetite</t>
         </is>
       </c>
     </row>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_11,_'label':_'loss_of_water'}</t>
+          <t>loss_of_water</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 11, 'label': 'loss_of_water'}</t>
+          <t>loss of water</t>
         </is>
       </c>
     </row>
@@ -1364,12 +1364,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_12,_'label':_'loss_of_energy'}</t>
+          <t>loss_of_energy</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 12, 'label': 'loss_of_energy'}</t>
+          <t>loss of energy</t>
         </is>
       </c>
     </row>
@@ -1381,12 +1381,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_13,_'label':_'loss_of_focus'}</t>
+          <t>loss_of_focus</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 13, 'label': 'loss_of_focus'}</t>
+          <t>loss of focus</t>
         </is>
       </c>
     </row>
@@ -1398,12 +1398,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_14,_'label':_'loss_of_memory'}</t>
+          <t>loss_of_memory</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 14, 'label': 'loss_of_memory'}</t>
+          <t>loss of memory</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_15,_'label':_'loss_of_sleep'}</t>
+          <t>loss_of_sleep</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 15, 'label': 'loss_of_sleep'}</t>
+          <t>loss of sleep</t>
         </is>
       </c>
     </row>
@@ -1432,12 +1432,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_16,_'label':_'loss_of_concentration'}</t>
+          <t>loss_of_concentration</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 16, 'label': 'loss_of_concentration'}</t>
+          <t>loss of concentration</t>
         </is>
       </c>
     </row>
@@ -1449,12 +1449,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_17,_'label':_'loss_of_appetite'}</t>
+          <t>loss_of_hunger</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 17, 'label': 'loss_of_appetite'}</t>
+          <t>loss of hunger</t>
         </is>
       </c>
     </row>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_18,_'label':_'loss_of_hunger'}</t>
+          <t>loss_of_thirst</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 18, 'label': 'loss_of_hunger'}</t>
+          <t>loss of thirst</t>
         </is>
       </c>
     </row>
@@ -1483,12 +1483,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_19,_'label':_'loss_of_thirst'}</t>
+          <t>loss_of_motivation</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 19, 'label': 'loss_of_thirst'}</t>
+          <t>loss of motivation</t>
         </is>
       </c>
     </row>
@@ -1500,12 +1500,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_20,_'label':_'loss_of_motivation'}</t>
+          <t>loss_of_interest</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 20, 'label': 'loss_of_motivation'}</t>
+          <t>loss of interest</t>
         </is>
       </c>
     </row>
@@ -1517,12 +1517,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_21,_'label':_'loss_of_interest'}</t>
+          <t>loss_of_confidence</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 21, 'label': 'loss_of_interest'}</t>
+          <t>loss of confidence</t>
         </is>
       </c>
     </row>
@@ -1534,12 +1534,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_22,_'label':_'loss_of_confidence'}</t>
+          <t>loss_of_self_esteem</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 22, 'label': 'loss_of_confidence'}</t>
+          <t>loss of self esteem</t>
         </is>
       </c>
     </row>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_23,_'label':_'loss_of_self_esteem'}</t>
+          <t>loss_of_identity</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 23, 'label': 'loss_of_self esteem'}</t>
+          <t>loss of identity</t>
         </is>
       </c>
     </row>
@@ -1568,12 +1568,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_24,_'label':_'loss_of_identity'}</t>
+          <t>loss_of_self</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 24, 'label': 'loss_of_identity'}</t>
+          <t>loss of self</t>
         </is>
       </c>
     </row>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_25,_'label':_'loss_of_self'}</t>
+          <t>loss_of_self_image</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 25, 'label': 'loss_of_self'}</t>
+          <t>loss of self image</t>
         </is>
       </c>
     </row>
@@ -1602,12 +1602,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_26,_'label':_'loss_of_self_image'}</t>
+          <t>loss_of_self_concept</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 26, 'label': 'loss_of_self_image'}</t>
+          <t>loss of self concept</t>
         </is>
       </c>
     </row>
@@ -1619,12 +1619,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_27,_'label':_'loss_of_self_concept'}</t>
+          <t>loss_of_self_image_schema</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 27, 'label': 'loss_of_self_concept'}</t>
+          <t>loss of self image schema</t>
         </is>
       </c>
     </row>
@@ -1636,12 +1636,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_28,_'label':_'loss_of_self_image_schema'}</t>
+          <t>loss_of_self_concept_schema</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 28, 'label': 'loss_of_self_image_schema'}</t>
+          <t>loss of self concept schema</t>
         </is>
       </c>
     </row>
@@ -1653,12 +1653,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_29,_'label':_'loss_of_self_concept_schema'}</t>
+          <t>loss_of_self_theory</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 29, 'label': 'loss_of_self_concept_schema'}</t>
+          <t>loss of self theory</t>
         </is>
       </c>
     </row>
@@ -1670,12 +1670,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_30,_'label':_'loss_of_self_theory'}</t>
+          <t>loss_of_self_identity</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 30, 'label': 'loss_of_self_theory'}</t>
+          <t>loss of self identity</t>
         </is>
       </c>
     </row>
@@ -1687,12 +1687,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_31,_'label':_'loss_of_self_identity'}</t>
+          <t>loss_of_self_confidence</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 31, 'label': 'loss_of_self_identity'}</t>
+          <t>loss of self confidence</t>
         </is>
       </c>
     </row>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_32,_'label':_'loss_of_self_confidence'}</t>
+          <t>loss_of_self_schema</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 32, 'label': 'loss_of_self_confidence'}</t>
+          <t>loss of self schema</t>
         </is>
       </c>
     </row>
@@ -1721,12 +1721,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_33,_'label':_'loss_of_self_concept_schema'}</t>
+          <t>loss_of_self_schema_theory</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 33, 'label': 'loss_of_self_concept_schema'}</t>
+          <t>loss of self schema theory</t>
         </is>
       </c>
     </row>
@@ -1738,12 +1738,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_34,_'label':_'loss_of_self_schema'}</t>
+          <t>loss_of_self_concept_schema_theory</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 34, 'label': 'loss_of_self_schema'}</t>
+          <t>loss of self concept schema theory</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_35,_'label':_'loss_of_self_theory'}</t>
+          <t>loss_of_self_confidence_schema</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 35, 'label': 'loss_of_self_theory'}</t>
+          <t>loss of self confidence schema</t>
         </is>
       </c>
     </row>
@@ -1772,12 +1772,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_36,_'label':_'loss_of_self_schema_theory'}</t>
+          <t>loss_of_self_schema_confidence</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 36, 'label': 'loss_of_self_schema_theory'}</t>
+          <t>loss of self schema confidence</t>
         </is>
       </c>
     </row>
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_37,_'label':_'loss_of_self_concept_schema_theory'}</t>
+          <t>loss_of_self_theory_schema</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 37, 'label': 'loss_of_self_concept_schema_theory'}</t>
+          <t>loss of self theory schema</t>
         </is>
       </c>
     </row>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_38,_'label':_'loss_of_self_confidence_schema'}</t>
+          <t>loss_of_self_confidence_schema_theory</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 38, 'label': 'loss_of_self_confidence_schema'}</t>
+          <t>loss of self confidence schema theory</t>
         </is>
       </c>
     </row>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_39,_'label':_'loss_of_self_schema_confidence'}</t>
+          <t>loss_of_self_concept_theory</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 39, 'label': 'loss_of_self_schema_confidence'}</t>
+          <t>loss of self concept theory</t>
         </is>
       </c>
     </row>
@@ -1840,12 +1840,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_40,_'label':_'loss_of_self_theory_schema'}</t>
+          <t>loss_of_self_theory_schema_confidence</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 40, 'label': 'loss_of_self_theory_schema'}</t>
+          <t>loss of self theory schema confidence</t>
         </is>
       </c>
     </row>
@@ -1857,12 +1857,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'id':_41,_'label':_'loss_of_self_concept_schema_theory'}</t>
+          <t>loss_of_self_schema_confidence_theory</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'id': 41, 'label': 'loss_of_self_concept_schema_theory'}</t>
+          <t>loss of self schema confidence theory</t>
         </is>
       </c>
     </row>
@@ -1874,148 +1874,148 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'id':_42,_'label':_'loss_of_self_schema_theory'}</t>
+          <t>loss_of_self_theory_schema_confidence_theory</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'id': 42, 'label': 'loss_of_self_schema_theory'}</t>
+          <t>loss of self theory schema confidence theory</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>symptoms_choices</t>
+          <t>treatment_option_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'id':_43,_'label':_'loss_of_self_confidence_schema_theory'}</t>
+          <t>medication</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'id': 43, 'label': 'loss_of_self_confidence_schema_theory'}</t>
+          <t>medication</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>symptoms_choices</t>
+          <t>treatment_option_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'id':_44,_'label':_'loss_of_self_schema_confidence'}</t>
+          <t>rest</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'id': 44, 'label': 'loss_of_self_schema_confidence'}</t>
+          <t>rest</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>symptoms_choices</t>
+          <t>treatment_option_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'id':_45,_'label':_'loss_of_self_theory_schema'}</t>
+          <t>exercise</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'id': 45, 'label': 'loss_of_self_theory_schema'}</t>
+          <t>exercise</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>symptoms_choices</t>
+          <t>treatment_option_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'id':_46,_'label':_'loss_of_self_concept_theory'}</t>
+          <t>therapy</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'id': 46, 'label': 'loss_of_self_concept_theory'}</t>
+          <t>therapy</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>symptoms_choices</t>
+          <t>treatment_option_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'id':_47,_'label':_'loss_of_self_theory_schema_confidence'}</t>
+          <t>surgery</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'id': 47, 'label': 'loss_of_self_theory_schema_confidence'}</t>
+          <t>surgery</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>symptoms_choices</t>
+          <t>treatment_option_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'id':_48,_'label':_'loss_of_self_schema_confidence_theory'}</t>
+          <t>hospitalization</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'id': 48, 'label': 'loss_of_self_schema_confidence_theory'}</t>
+          <t>hospitalization</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>symptoms_choices</t>
+          <t>treatment_option_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'id':_49,_'label':_'loss_of_self_theory_schema_confidence_theory'}</t>
+          <t>self_care</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'id': 49, 'label': 'loss_of_self_theory_schema_confidence_theory'}</t>
+          <t>self care</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>symptoms_choices</t>
+          <t>treatment_option_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'id':_50,_'label':_'loss_of_self_confidence_schema_theory'}</t>
+          <t>diet</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'id': 50, 'label': 'loss_of_self_confidence_schema_theory'}</t>
+          <t>diet</t>
         </is>
       </c>
     </row>
@@ -2027,12 +2027,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'medication'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'medication'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -2044,12 +2044,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'rest'}</t>
+          <t>follow_up</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'rest'}</t>
+          <t>follow up</t>
         </is>
       </c>
     </row>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'exercise'}</t>
+          <t>monitor</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'exercise'}</t>
+          <t>monitor</t>
         </is>
       </c>
     </row>
@@ -2078,12 +2078,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'therapy'}</t>
+          <t>refer</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'therapy'}</t>
+          <t>refer</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'surgery'}</t>
+          <t>other_treatment</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'surgery'}</t>
+          <t>other treatment</t>
         </is>
       </c>
     </row>
@@ -2112,12 +2112,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'hospitalization'}</t>
+          <t>hospital_treatment</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'hospitalization'}</t>
+          <t>hospital treatment</t>
         </is>
       </c>
     </row>
@@ -2129,148 +2129,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'self_care'}</t>
+          <t>clinic_treatment</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'self_care'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>treatment_option_choices</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>{'id':_8,_'label':_'diet'}</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>{'id': 8, 'label': 'diet'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>treatment_option_choices</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>{'id':_9,_'label':_'other'}</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>{'id': 9, 'label': 'other'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>treatment_option_choices</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>{'id':_10,_'label':_'follow_up'}</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>{'id': 10, 'label': 'follow_up'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>treatment_option_choices</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>{'id':_11,_'label':_'monitor'}</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>{'id': 11, 'label': 'monitor'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>treatment_option_choices</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>{'id':_12,_'label':_'refer'}</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>{'id': 12, 'label': 'refer'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>treatment_option_choices</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>{'id':_13,_'label':_'other_treatment'}</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>{'id': 13, 'label': 'other_treatment'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>treatment_option_choices</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>{'id':_14,_'label':_'hospital_treatment'}</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>{'id': 14, 'label': 'hospital_treatment'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>treatment_option_choices</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>{'id':_15,_'label':_'clinic_treatment'}</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>{'id': 15, 'label': 'clinic_treatment'}</t>
+          <t>clinic treatment</t>
         </is>
       </c>
     </row>
